--- a/Catch models/consistence_table_macarellus_cmsy.xlsx
+++ b/Catch models/consistence_table_macarellus_cmsy.xlsx
@@ -46,13 +46,13 @@
     <t>Decapterus macarellus_NA</t>
   </si>
   <si>
-    <t>0.96 [0.73-1.01]</t>
-  </si>
-  <si>
-    <t>0.36 [0.32-0.51]</t>
-  </si>
-  <si>
-    <t>Overfished but not overfishing</t>
+    <t>0.43 [0.39-0.53]</t>
+  </si>
+  <si>
+    <t>1.19 [0.90-1.45]</t>
+  </si>
+  <si>
+    <t>Overfished and overfishing</t>
   </si>
   <si>
     <t>Moderate</t>
@@ -441,16 +441,16 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>68.8</v>
+        <v>37.5</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>62.5</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>

--- a/Catch models/consistence_table_macarellus_cmsy.xlsx
+++ b/Catch models/consistence_table_macarellus_cmsy.xlsx
@@ -46,10 +46,10 @@
     <t>Decapterus macarellus_NA</t>
   </si>
   <si>
-    <t>0.43 [0.39-0.53]</t>
-  </si>
-  <si>
-    <t>1.19 [0.90-1.45]</t>
+    <t>0.38 [0.33-0.45]</t>
+  </si>
+  <si>
+    <t>1.23 [1.03-1.66]</t>
   </si>
   <si>
     <t>Overfished and overfishing</t>
@@ -447,10 +447,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>

--- a/Catch models/consistence_table_macarellus_cmsy.xlsx
+++ b/Catch models/consistence_table_macarellus_cmsy.xlsx
@@ -46,10 +46,10 @@
     <t>Decapterus macarellus_NA</t>
   </si>
   <si>
-    <t>0.38 [0.33-0.45]</t>
-  </si>
-  <si>
-    <t>1.23 [1.03-1.66]</t>
+    <t>0.37 [0.32-0.44]</t>
+  </si>
+  <si>
+    <t>1.37 [0.99-1.69]</t>
   </si>
   <si>
     <t>Overfished and overfishing</t>

--- a/Catch models/consistence_table_macarellus_cmsy.xlsx
+++ b/Catch models/consistence_table_macarellus_cmsy.xlsx
@@ -46,16 +46,16 @@
     <t>Decapterus macarellus_NA</t>
   </si>
   <si>
-    <t>0.37 [0.32-0.44]</t>
-  </si>
-  <si>
-    <t>1.37 [0.99-1.69]</t>
-  </si>
-  <si>
-    <t>Overfished and overfishing</t>
-  </si>
-  <si>
-    <t>Moderate</t>
+    <t>0.49 [0.37-0.58]</t>
+  </si>
+  <si>
+    <t>0.27 [0.21-0.44]</t>
+  </si>
+  <si>
+    <t>Overfished but not overfishing</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -441,16 +441,16 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>93.8</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
